--- a/outputs/deepseek_v4_flash_910b_910c_8card_estimate.xlsx
+++ b/outputs/deepseek_v4_flash_910b_910c_8card_estimate.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,41 +485,137 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P800实测基线 + 模型差异 + 硬件Roofline比例</t>
+          <t>P800实测基线 + R1 INT8基线模型 -&gt; V4 Flash INT8目标模型 + 硬件Roofline比例</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>910B参考数据</t>
+          <t>P800显存口径</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>只进入参考sheet，不参与校准</t>
+          <t>按用户确认的实测P800 96GB写入假设表；未采用项目旧seed中的64GB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>联网参考数据</t>
+          <t>目标模型口径</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>只进入联网参考sheet，不参与校准</t>
+          <t>DeepSeek V4-Flash按公开Hugging Face模型卡284B总参数、13B激活参数；如内部口径为283B/14B，可替换假设后重算</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>显存公式</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>required_per_card_gb = total_params_b*1e9*weight_bytes/1024^3/gpu_count + KV_cache_gb/gpu_count + framework_overhead_gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Decode公式</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>decode_scale = min(compute_scale, bandwidth_scale); throughput_target = throughput_base * decode_scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>compute_scale</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(target_tflops*target_eff)/(base_tflops*base_eff) * (base_active_params_b/target_active_params_b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bandwidth_scale</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(target_bw*target_eff)/(base_bw*base_eff) * (base_decode_bytes_per_token/target_decode_bytes_per_token)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TTFT公式</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ttft_target = ttft_base / prefill_compute_scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>增量时延公式</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>decode_latency_target = decode_latency_base / decode_scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>910B参考数据</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>只进入参考sheet，不参与校准</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>联网参考数据</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>公开硬件规格进入公式假设；公开吞吐/benchmark只进入参考sheet，不参与校准</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>适用边界</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>估算不能替代实测；实际部署需用910B/910C复测</t>
         </is>
@@ -536,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +679,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n">
         <v>2000</v>
@@ -593,7 +689,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>project_seed_data</t>
+          <t>user_confirmed_p800_96gb</t>
         </is>
       </c>
     </row>
@@ -718,12 +814,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>model_base</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeepSeek v4 flash proxy</t>
+          <t>DeepSeek R1 INT8 baseline proxy</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -737,7 +833,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>model_target</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Flash INT8 public proxy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>284</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture</t>
         </is>
       </c>
     </row>
@@ -887,15 +1009,33 @@
       <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>281.3141</v>
+      </c>
+      <c r="E2" t="n">
+        <v>169.1862</v>
+      </c>
+      <c r="F2" t="n">
+        <v>177.7843</v>
+      </c>
+      <c r="G2" t="n">
+        <v>177.7985</v>
+      </c>
+      <c r="H2" t="n">
+        <v>135.4762</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18.0831</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.3852</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19.1916</v>
+      </c>
+      <c r="L2" t="n">
+        <v>17.5998</v>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -916,28 +1056,28 @@
         <v>0.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2.404053</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2.404053</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>84.68859999999999</v>
+        <v>39.6359</v>
       </c>
       <c r="W2" t="n">
         <v>0.78</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -951,15 +1091,33 @@
       <c r="C3" t="n">
         <v>10</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>427.667</v>
+      </c>
+      <c r="E3" t="n">
+        <v>258.0897</v>
+      </c>
+      <c r="F3" t="n">
+        <v>332.7442</v>
+      </c>
+      <c r="G3" t="n">
+        <v>332.7759</v>
+      </c>
+      <c r="H3" t="n">
+        <v>187.5236</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23.8183</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.1772</v>
+      </c>
+      <c r="K3" t="n">
+        <v>25.5763</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.149</v>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -980,28 +1138,28 @@
         <v>0.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2.404047</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2.404047</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>88.2627</v>
+        <v>43.2099</v>
       </c>
       <c r="W3" t="n">
         <v>0.78</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1015,15 +1173,33 @@
       <c r="C4" t="n">
         <v>15</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>550.8957</v>
+      </c>
+      <c r="E4" t="n">
+        <v>433.0719</v>
+      </c>
+      <c r="F4" t="n">
+        <v>433.3456</v>
+      </c>
+      <c r="G4" t="n">
+        <v>433.3949</v>
+      </c>
+      <c r="H4" t="n">
+        <v>235.3281</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27.6937</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.191</v>
+      </c>
+      <c r="K4" t="n">
+        <v>31.0377</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.9323</v>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -1044,28 +1220,28 @@
         <v>0.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>91.837</v>
+        <v>46.7843</v>
       </c>
       <c r="W4" t="n">
         <v>0.78</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1079,15 +1255,33 @@
       <c r="C5" t="n">
         <v>20</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>661.3773</v>
+      </c>
+      <c r="E5" t="n">
+        <v>465.4754</v>
+      </c>
+      <c r="F5" t="n">
+        <v>568.8253999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>568.8801999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>280.3632</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30.7823</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.2024</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32.7841</v>
+      </c>
+      <c r="L5" t="n">
+        <v>29.8714</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -1108,28 +1302,28 @@
         <v>0.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2.404053</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2.404053</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>95.41030000000001</v>
+        <v>50.3576</v>
       </c>
       <c r="W5" t="n">
         <v>0.78</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1143,15 +1337,33 @@
       <c r="C6" t="n">
         <v>25</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>757.5479</v>
+      </c>
+      <c r="E6" t="n">
+        <v>600.9859</v>
+      </c>
+      <c r="F6" t="n">
+        <v>676.5694999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>676.5907999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>316.0137</v>
+      </c>
+      <c r="I6" t="n">
+        <v>33.7441</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.3003</v>
+      </c>
+      <c r="K6" t="n">
+        <v>35.371</v>
+      </c>
+      <c r="L6" t="n">
+        <v>32.5768</v>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -1172,28 +1384,28 @@
         <v>0.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2.404033</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2.404033</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>98.98560000000001</v>
+        <v>53.9329</v>
       </c>
       <c r="W6" t="n">
         <v>0.78</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1207,15 +1419,33 @@
       <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>841.3771</v>
+      </c>
+      <c r="E7" t="n">
+        <v>689.0739</v>
+      </c>
+      <c r="F7" t="n">
+        <v>820.8183</v>
+      </c>
+      <c r="G7" t="n">
+        <v>820.8328</v>
+      </c>
+      <c r="H7" t="n">
+        <v>362.0701</v>
+      </c>
+      <c r="I7" t="n">
+        <v>36.575</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.0969</v>
+      </c>
+      <c r="K7" t="n">
+        <v>38.7349</v>
+      </c>
+      <c r="L7" t="n">
+        <v>35.1548</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -1236,28 +1466,28 @@
         <v>0.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>102.5594</v>
+        <v>57.5066</v>
       </c>
       <c r="W7" t="n">
         <v>0.78</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1300,13 +1530,13 @@
         <v>0.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2.404042</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2.404042</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1314,14 +1544,14 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>106.1331</v>
+        <v>61.0804</v>
       </c>
       <c r="W8" t="n">
         <v>0.78</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1594,13 @@
         <v>0.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1378,14 +1608,14 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>109.7077</v>
+        <v>64.6549</v>
       </c>
       <c r="W9" t="n">
         <v>0.78</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1428,13 +1658,13 @@
         <v>0.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2.404037</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2.404037</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1442,14 +1672,14 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>113.2819</v>
+        <v>68.2291</v>
       </c>
       <c r="W10" t="n">
         <v>0.78</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1492,13 +1722,13 @@
         <v>0.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2.404041</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2.404041</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1506,14 +1736,14 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>116.8555</v>
+        <v>71.8027</v>
       </c>
       <c r="W11" t="n">
         <v>0.78</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1556,13 +1786,13 @@
         <v>0.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2.404048</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2.404048</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1570,14 +1800,14 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>120.4285</v>
+        <v>75.37569999999999</v>
       </c>
       <c r="W12" t="n">
         <v>0.78</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1620,13 +1850,13 @@
         <v>0.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2.40404</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2.40404</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1634,14 +1864,14 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>124.0038</v>
+        <v>78.95099999999999</v>
       </c>
       <c r="W13" t="n">
         <v>0.78</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1684,13 +1914,13 @@
         <v>0.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2.404042</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2.404042</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1698,14 +1928,14 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>126.8627</v>
+        <v>81.8099</v>
       </c>
       <c r="W14" t="n">
         <v>0.78</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1748,13 +1978,13 @@
         <v>0.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2.404036</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2.404036</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1762,14 +1992,14 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>149.7383</v>
+        <v>104.6856</v>
       </c>
       <c r="W15" t="n">
         <v>0.78</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1812,13 +2042,13 @@
         <v>0.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2.404038</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1826,14 +2056,14 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>172.612</v>
+        <v>127.5593</v>
       </c>
       <c r="W16" t="n">
         <v>0.78</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1847,15 +2077,33 @@
       <c r="C17" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>257.9372</v>
+      </c>
+      <c r="E17" t="n">
+        <v>284.1901</v>
+      </c>
+      <c r="F17" t="n">
+        <v>348.4338</v>
+      </c>
+      <c r="G17" t="n">
+        <v>358.8882</v>
+      </c>
+      <c r="H17" t="n">
+        <v>178.4374</v>
+      </c>
+      <c r="I17" t="n">
+        <v>19.5858</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19.8875</v>
+      </c>
+      <c r="K17" t="n">
+        <v>21.0628</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19.1343</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -1876,28 +2124,28 @@
         <v>0.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2.253888</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2.253888</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>85.88030000000001</v>
+        <v>40.8276</v>
       </c>
       <c r="W17" t="n">
         <v>0.78</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1911,15 +2159,33 @@
       <c r="C18" t="n">
         <v>10</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>394.8163</v>
+      </c>
+      <c r="E18" t="n">
+        <v>487.9337</v>
+      </c>
+      <c r="F18" t="n">
+        <v>570.1042</v>
+      </c>
+      <c r="G18" t="n">
+        <v>570.1395</v>
+      </c>
+      <c r="H18" t="n">
+        <v>242.7782</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25.7272</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26.2237</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26.8477</v>
+      </c>
+      <c r="L18" t="n">
+        <v>24.9842</v>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -1940,28 +2206,28 @@
         <v>0.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2.253888</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2.253888</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>90.6459</v>
+        <v>45.5932</v>
       </c>
       <c r="W18" t="n">
         <v>0.78</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -1975,15 +2241,33 @@
       <c r="C19" t="n">
         <v>15</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>502.2751</v>
+      </c>
+      <c r="E19" t="n">
+        <v>699.5796</v>
+      </c>
+      <c r="F19" t="n">
+        <v>829.8089</v>
+      </c>
+      <c r="G19" t="n">
+        <v>829.8453</v>
+      </c>
+      <c r="H19" t="n">
+        <v>318.1646</v>
+      </c>
+      <c r="I19" t="n">
+        <v>30.3529</v>
+      </c>
+      <c r="J19" t="n">
+        <v>30.8176</v>
+      </c>
+      <c r="K19" t="n">
+        <v>32.5539</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29.3842</v>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -2004,28 +2288,28 @@
         <v>0.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2.253894</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2.253894</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>95.41119999999999</v>
+        <v>50.3585</v>
       </c>
       <c r="W19" t="n">
         <v>0.78</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2039,15 +2323,33 @@
       <c r="C20" t="n">
         <v>20</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>596.3384</v>
+      </c>
+      <c r="E20" t="n">
+        <v>909.9378</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1049.2349</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1049.3298</v>
+      </c>
+      <c r="H20" t="n">
+        <v>385.8378</v>
+      </c>
+      <c r="I20" t="n">
+        <v>34.1189</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.5445</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35.9208</v>
+      </c>
+      <c r="L20" t="n">
+        <v>32.9443</v>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -2068,28 +2370,28 @@
         <v>0.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2.253895</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2.253895</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>100.1767</v>
+        <v>55.124</v>
       </c>
       <c r="W20" t="n">
         <v>0.78</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2132,13 +2434,13 @@
         <v>0.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>2.253888</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2.253888</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2146,14 +2448,14 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>104.9428</v>
+        <v>59.8901</v>
       </c>
       <c r="W21" t="n">
         <v>0.78</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2196,13 +2498,13 @@
         <v>0.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2.253896</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2.253896</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2210,14 +2512,14 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>109.7077</v>
+        <v>64.6549</v>
       </c>
       <c r="W22" t="n">
         <v>0.78</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2260,13 +2562,13 @@
         <v>0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>2.253892</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2.253892</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2274,14 +2576,14 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>114.4736</v>
+        <v>69.4209</v>
       </c>
       <c r="W23" t="n">
         <v>0.78</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2324,13 +2626,13 @@
         <v>0.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2.253892</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2.253892</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2338,14 +2640,14 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>119.2392</v>
+        <v>74.1865</v>
       </c>
       <c r="W24" t="n">
         <v>0.78</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2388,13 +2690,13 @@
         <v>0.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>2.253897</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2.253897</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2402,14 +2704,14 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>124.0039</v>
+        <v>78.9512</v>
       </c>
       <c r="W25" t="n">
         <v>0.78</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2452,13 +2754,13 @@
         <v>0.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>2.25389</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2.25389</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2466,14 +2768,14 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>128.7706</v>
+        <v>83.7179</v>
       </c>
       <c r="W26" t="n">
         <v>0.78</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2516,13 +2818,13 @@
         <v>0.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2.253895</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2.253895</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -2530,14 +2832,14 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>133.5353</v>
+        <v>88.48260000000001</v>
       </c>
       <c r="W27" t="n">
         <v>0.78</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2580,13 +2882,13 @@
         <v>0.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2.25389</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2.25389</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -2594,14 +2896,14 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>138.3019</v>
+        <v>93.2491</v>
       </c>
       <c r="W28" t="n">
         <v>0.78</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2946,13 @@
         <v>0.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>2.253892</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2.253892</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -2658,14 +2960,14 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>142.1139</v>
+        <v>97.0612</v>
       </c>
       <c r="W29" t="n">
         <v>0.78</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2708,13 +3010,13 @@
         <v>0.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2.253891</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2.253891</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -2722,14 +3024,14 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>172.6139</v>
+        <v>127.5612</v>
       </c>
       <c r="W30" t="n">
         <v>0.78</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2743,15 +3045,33 @@
       <c r="C31" t="n">
         <v>5</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>222.7792</v>
+      </c>
+      <c r="E31" t="n">
+        <v>502.4314</v>
+      </c>
+      <c r="F31" t="n">
+        <v>555.0997</v>
+      </c>
+      <c r="G31" t="n">
+        <v>555.1191</v>
+      </c>
+      <c r="H31" t="n">
+        <v>225.3686</v>
+      </c>
+      <c r="I31" t="n">
+        <v>22.6114</v>
+      </c>
+      <c r="J31" t="n">
+        <v>22.9939</v>
+      </c>
+      <c r="K31" t="n">
+        <v>23.5662</v>
+      </c>
+      <c r="L31" t="n">
+        <v>22.0856</v>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -2772,28 +3092,28 @@
         <v>0.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>2.032964</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2.032964</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>88.26309999999999</v>
+        <v>43.2104</v>
       </c>
       <c r="W31" t="n">
         <v>0.78</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2807,15 +3127,33 @@
       <c r="C32" t="n">
         <v>10</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>333.5841</v>
+      </c>
+      <c r="E32" t="n">
+        <v>984.0796</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1118.2355</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1118.2743</v>
+      </c>
+      <c r="H32" t="n">
+        <v>365.8148</v>
+      </c>
+      <c r="I32" t="n">
+        <v>30.1125</v>
+      </c>
+      <c r="J32" t="n">
+        <v>30.4932</v>
+      </c>
+      <c r="K32" t="n">
+        <v>30.955</v>
+      </c>
+      <c r="L32" t="n">
+        <v>29.3502</v>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -2836,28 +3174,28 @@
         <v>0.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>2.032973</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2.032973</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>95.4111</v>
+        <v>50.3584</v>
       </c>
       <c r="W32" t="n">
         <v>0.78</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2871,15 +3209,33 @@
       <c r="C33" t="n">
         <v>15</v>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>421.7669</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1335.8295</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1680.2726</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1713.995</v>
+      </c>
+      <c r="H33" t="n">
+        <v>495.089</v>
+      </c>
+      <c r="I33" t="n">
+        <v>35.586</v>
+      </c>
+      <c r="J33" t="n">
+        <v>36.1621</v>
+      </c>
+      <c r="K33" t="n">
+        <v>37.0605</v>
+      </c>
+      <c r="L33" t="n">
+        <v>34.6485</v>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -2900,28 +3256,28 @@
         <v>0.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>2.032966</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2.032966</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>102.5598</v>
+        <v>57.5071</v>
       </c>
       <c r="W33" t="n">
         <v>0.78</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -2964,13 +3320,13 @@
         <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>2.032964</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2.032964</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -2978,14 +3334,14 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>109.7084</v>
+        <v>64.6557</v>
       </c>
       <c r="W34" t="n">
         <v>0.78</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3028,13 +3384,13 @@
         <v>0.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>2.032967</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2.032967</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -3042,14 +3398,14 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>116.8566</v>
+        <v>71.8038</v>
       </c>
       <c r="W35" t="n">
         <v>0.78</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3092,13 +3448,13 @@
         <v>0.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2.032973</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>2.032973</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -3106,14 +3462,14 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>124.0039</v>
+        <v>78.9512</v>
       </c>
       <c r="W36" t="n">
         <v>0.78</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3156,13 +3512,13 @@
         <v>0.7</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>2.032964</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2.032964</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -3170,14 +3526,14 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>131.1537</v>
+        <v>86.101</v>
       </c>
       <c r="W37" t="n">
         <v>0.78</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3220,13 +3576,13 @@
         <v>0.7</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>2.032968</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>2.032968</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -3234,14 +3590,14 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>138.3014</v>
+        <v>93.2487</v>
       </c>
       <c r="W38" t="n">
         <v>0.78</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3284,13 +3640,13 @@
         <v>0.7</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>2.03297</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2.03297</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -3298,14 +3654,14 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>145.4494</v>
+        <v>100.3966</v>
       </c>
       <c r="W39" t="n">
         <v>0.78</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3348,13 +3704,13 @@
         <v>0.7</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>2.032966</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2.032966</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -3362,14 +3718,14 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>152.5986</v>
+        <v>107.5459</v>
       </c>
       <c r="W40" t="n">
         <v>0.78</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3383,15 +3739,33 @@
       <c r="C41" t="n">
         <v>5</v>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>177.6175</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1059.5663</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1221.085</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1232.148</v>
+      </c>
+      <c r="H41" t="n">
+        <v>364.8048</v>
+      </c>
+      <c r="I41" t="n">
+        <v>28.1348</v>
+      </c>
+      <c r="J41" t="n">
+        <v>28.5544</v>
+      </c>
+      <c r="K41" t="n">
+        <v>29.2286</v>
+      </c>
+      <c r="L41" t="n">
+        <v>27.4166</v>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -3412,28 +3786,28 @@
         <v>0.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>1.763814</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>1.763814</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>93.0286</v>
+        <v>47.9759</v>
       </c>
       <c r="W41" t="n">
         <v>0.78</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3850,13 @@
         <v>0.7</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>1.763811</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>1.763811</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -3490,14 +3864,14 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>104.9428</v>
+        <v>59.8901</v>
       </c>
       <c r="W42" t="n">
         <v>0.78</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3540,13 +3914,13 @@
         <v>0.7</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>1.763819</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>1.763819</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -3554,14 +3928,14 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>116.8558</v>
+        <v>71.8031</v>
       </c>
       <c r="W43" t="n">
         <v>0.78</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3604,13 +3978,13 @@
         <v>0.7</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>1.763811</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>1.763811</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -3618,14 +3992,14 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>128.7709</v>
+        <v>83.7182</v>
       </c>
       <c r="W44" t="n">
         <v>0.78</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3668,13 +4042,13 @@
         <v>0.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>1.763811</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>1.763811</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -3682,14 +4056,14 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>140.685</v>
+        <v>95.6323</v>
       </c>
       <c r="W45" t="n">
         <v>0.78</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3703,15 +4077,33 @@
       <c r="C46" t="n">
         <v>5</v>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>151.3883</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1537.8066</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1872.4396</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1894.7331</v>
+      </c>
+      <c r="H46" t="n">
+        <v>541.3184</v>
+      </c>
+      <c r="I46" t="n">
+        <v>32.6031</v>
+      </c>
+      <c r="J46" t="n">
+        <v>33.0592</v>
+      </c>
+      <c r="K46" t="n">
+        <v>33.6671</v>
+      </c>
+      <c r="L46" t="n">
+        <v>31.9016</v>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -3732,28 +4124,28 @@
         <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>1.605928</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>1.605928</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>97.7944</v>
+        <v>52.7416</v>
       </c>
       <c r="W46" t="n">
         <v>0.78</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3796,13 +4188,13 @@
         <v>0.7</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>1.605928</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>1.605928</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -3810,14 +4202,14 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>114.4741</v>
+        <v>69.4213</v>
       </c>
       <c r="W47" t="n">
         <v>0.78</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3860,13 +4252,13 @@
         <v>0.7</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>1.605929</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>1.605929</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -3874,14 +4266,14 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>131.1536</v>
+        <v>86.1009</v>
       </c>
       <c r="W48" t="n">
         <v>0.78</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3924,13 +4316,13 @@
         <v>0.7</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>1.605932</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>1.605932</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -3938,14 +4330,14 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>147.8323</v>
+        <v>102.7796</v>
       </c>
       <c r="W49" t="n">
         <v>0.78</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -3959,15 +4351,33 @@
       <c r="C50" t="n">
         <v>5</v>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>130.1264</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2151.0012</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2672.8928</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2723.226</v>
+      </c>
+      <c r="H50" t="n">
+        <v>714.7682</v>
+      </c>
+      <c r="I50" t="n">
+        <v>37.5936</v>
+      </c>
+      <c r="J50" t="n">
+        <v>38.1004</v>
+      </c>
+      <c r="K50" t="n">
+        <v>42.0708</v>
+      </c>
+      <c r="L50" t="n">
+        <v>36.8119</v>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -3988,28 +4398,28 @@
         <v>0.7</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>1.502137</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>1.502137</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>102.5597</v>
+        <v>57.507</v>
       </c>
       <c r="W50" t="n">
         <v>0.78</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4052,13 +4462,13 @@
         <v>0.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>1.502135</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>1.502135</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -4066,14 +4476,14 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>124.0052</v>
+        <v>78.9524</v>
       </c>
       <c r="W51" t="n">
         <v>0.78</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4116,13 +4526,13 @@
         <v>0.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>2.846154</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>1.502135</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>1.502135</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -4130,14 +4540,14 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>145.4505</v>
+        <v>100.3977</v>
       </c>
       <c r="W52" t="n">
         <v>0.78</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; p800_equivalent_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; p800_equivalent_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4288,31 +4698,31 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>234.0332</v>
+        <v>562.6282</v>
       </c>
       <c r="E2" t="n">
-        <v>170.9587</v>
+        <v>60.7335</v>
       </c>
       <c r="F2" t="n">
-        <v>179.6469</v>
+        <v>63.82</v>
       </c>
       <c r="G2" t="n">
-        <v>179.6612</v>
+        <v>63.8251</v>
       </c>
       <c r="H2" t="n">
-        <v>136.8956</v>
+        <v>48.6325</v>
       </c>
       <c r="I2" t="n">
-        <v>21.7364</v>
+        <v>9.041600000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>22.0996</v>
+        <v>9.192600000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>23.0689</v>
+        <v>9.595800000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>21.1554</v>
+        <v>8.799899999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -4334,13 +4744,13 @@
         <v>0.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4.808106</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>4.808106</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -4348,14 +4758,14 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>84.68859999999999</v>
+        <v>39.6359</v>
       </c>
       <c r="W2" t="n">
         <v>0.76</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4370,31 +4780,31 @@
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>355.7892</v>
+        <v>855.3341</v>
       </c>
       <c r="E3" t="n">
-        <v>260.7936</v>
+        <v>92.6476</v>
       </c>
       <c r="F3" t="n">
-        <v>336.2303</v>
+        <v>119.4466</v>
       </c>
       <c r="G3" t="n">
-        <v>336.2623</v>
+        <v>119.458</v>
       </c>
       <c r="H3" t="n">
-        <v>189.4882</v>
+        <v>67.31610000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>28.6302</v>
+        <v>11.9091</v>
       </c>
       <c r="J3" t="n">
-        <v>29.0616</v>
+        <v>12.0886</v>
       </c>
       <c r="K3" t="n">
-        <v>30.7433</v>
+        <v>12.7882</v>
       </c>
       <c r="L3" t="n">
-        <v>27.8256</v>
+        <v>11.5745</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -4416,13 +4826,13 @@
         <v>0.7</v>
       </c>
       <c r="R3" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4.808095</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>4.808095</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4430,14 +4840,14 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>88.2627</v>
+        <v>43.2099</v>
       </c>
       <c r="W3" t="n">
         <v>0.76</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4452,31 +4862,31 @@
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>458.3086</v>
+        <v>1101.7914</v>
       </c>
       <c r="E4" t="n">
-        <v>437.6092</v>
+        <v>155.4617</v>
       </c>
       <c r="F4" t="n">
-        <v>437.8856</v>
+        <v>155.5599</v>
       </c>
       <c r="G4" t="n">
-        <v>437.9355</v>
+        <v>155.5777</v>
       </c>
       <c r="H4" t="n">
-        <v>237.7936</v>
+        <v>84.4768</v>
       </c>
       <c r="I4" t="n">
-        <v>33.2884</v>
+        <v>13.8469</v>
       </c>
       <c r="J4" t="n">
-        <v>33.8861</v>
+        <v>14.0955</v>
       </c>
       <c r="K4" t="n">
-        <v>37.3079</v>
+        <v>15.5188</v>
       </c>
       <c r="L4" t="n">
-        <v>32.3732</v>
+        <v>13.4662</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -4498,13 +4908,13 @@
         <v>0.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -4512,14 +4922,14 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>91.837</v>
+        <v>46.7843</v>
       </c>
       <c r="W4" t="n">
         <v>0.76</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4534,31 +4944,31 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>550.2186</v>
+        <v>1322.7546</v>
       </c>
       <c r="E5" t="n">
-        <v>470.3521</v>
+        <v>167.0937</v>
       </c>
       <c r="F5" t="n">
-        <v>574.7849</v>
+        <v>204.1937</v>
       </c>
       <c r="G5" t="n">
-        <v>574.8402</v>
+        <v>204.2134</v>
       </c>
       <c r="H5" t="n">
-        <v>283.3006</v>
+        <v>100.6432</v>
       </c>
       <c r="I5" t="n">
-        <v>37.0011</v>
+        <v>15.3911</v>
       </c>
       <c r="J5" t="n">
-        <v>37.5061</v>
+        <v>15.6012</v>
       </c>
       <c r="K5" t="n">
-        <v>39.4073</v>
+        <v>16.392</v>
       </c>
       <c r="L5" t="n">
-        <v>35.9062</v>
+        <v>14.9357</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -4580,13 +4990,13 @@
         <v>0.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4.808106</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>4.808106</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -4594,14 +5004,14 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>95.41030000000001</v>
+        <v>50.3576</v>
       </c>
       <c r="W5" t="n">
         <v>0.76</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4616,31 +5026,31 @@
         <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>630.2308</v>
+        <v>1515.0957</v>
       </c>
       <c r="E6" t="n">
-        <v>607.2823</v>
+        <v>215.7385</v>
       </c>
       <c r="F6" t="n">
-        <v>683.6578</v>
+        <v>242.8711</v>
       </c>
       <c r="G6" t="n">
-        <v>683.6793</v>
+        <v>242.8787</v>
       </c>
       <c r="H6" t="n">
-        <v>319.3245</v>
+        <v>113.4408</v>
       </c>
       <c r="I6" t="n">
-        <v>40.5609</v>
+        <v>16.872</v>
       </c>
       <c r="J6" t="n">
-        <v>41.2295</v>
+        <v>17.1501</v>
       </c>
       <c r="K6" t="n">
-        <v>42.5165</v>
+        <v>17.6855</v>
       </c>
       <c r="L6" t="n">
-        <v>39.1579</v>
+        <v>16.2884</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -4662,13 +5072,13 @@
         <v>0.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4.808066</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>4.808066</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4676,14 +5086,14 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>98.98560000000001</v>
+        <v>53.9329</v>
       </c>
       <c r="W6" t="n">
         <v>0.76</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4698,31 +5108,31 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>699.9698</v>
+        <v>1682.7541</v>
       </c>
       <c r="E7" t="n">
-        <v>696.2932</v>
+        <v>247.3599</v>
       </c>
       <c r="F7" t="n">
-        <v>829.4179</v>
+        <v>294.6527</v>
       </c>
       <c r="G7" t="n">
-        <v>829.4325</v>
+        <v>294.6579</v>
       </c>
       <c r="H7" t="n">
-        <v>365.8634</v>
+        <v>129.9739</v>
       </c>
       <c r="I7" t="n">
-        <v>43.9639</v>
+        <v>18.2875</v>
       </c>
       <c r="J7" t="n">
-        <v>44.5912</v>
+        <v>18.5485</v>
       </c>
       <c r="K7" t="n">
-        <v>46.56</v>
+        <v>19.3674</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2568</v>
+        <v>17.5774</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -4744,13 +5154,13 @@
         <v>0.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -4758,14 +5168,14 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>102.5594</v>
+        <v>57.5066</v>
       </c>
       <c r="W7" t="n">
         <v>0.76</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4780,31 +5190,31 @@
         <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>775.4654</v>
+        <v>1864.2513</v>
       </c>
       <c r="E8" t="n">
-        <v>674.8199</v>
+        <v>239.7314</v>
       </c>
       <c r="F8" t="n">
-        <v>952.5884</v>
+        <v>338.4094</v>
       </c>
       <c r="G8" t="n">
-        <v>955.7494</v>
+        <v>339.5323</v>
       </c>
       <c r="H8" t="n">
-        <v>399.9808</v>
+        <v>142.0942</v>
       </c>
       <c r="I8" t="n">
-        <v>46.3697</v>
+        <v>19.2882</v>
       </c>
       <c r="J8" t="n">
-        <v>47.0374</v>
+        <v>19.566</v>
       </c>
       <c r="K8" t="n">
-        <v>49.1351</v>
+        <v>20.4385</v>
       </c>
       <c r="L8" t="n">
-        <v>44.4149</v>
+        <v>18.4751</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -4826,13 +5236,13 @@
         <v>0.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4.808084</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>4.808084</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -4840,14 +5250,14 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>106.1331</v>
+        <v>61.0804</v>
       </c>
       <c r="W8" t="n">
         <v>0.76</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4862,31 +5272,31 @@
         <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>836.6682</v>
+        <v>2011.3819</v>
       </c>
       <c r="E9" t="n">
-        <v>884.5888</v>
+        <v>314.2523</v>
       </c>
       <c r="F9" t="n">
-        <v>1040.8119</v>
+        <v>369.751</v>
       </c>
       <c r="G9" t="n">
-        <v>1040.9496</v>
+        <v>369.7999</v>
       </c>
       <c r="H9" t="n">
-        <v>426.7244</v>
+        <v>151.5949</v>
       </c>
       <c r="I9" t="n">
-        <v>49.0519</v>
+        <v>20.404</v>
       </c>
       <c r="J9" t="n">
-        <v>49.6808</v>
+        <v>20.6655</v>
       </c>
       <c r="K9" t="n">
-        <v>52.5735</v>
+        <v>21.8688</v>
       </c>
       <c r="L9" t="n">
-        <v>47.0339</v>
+        <v>19.5646</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -4908,13 +5318,13 @@
         <v>0.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4922,14 +5332,14 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>109.7077</v>
+        <v>64.6549</v>
       </c>
       <c r="W9" t="n">
         <v>0.76</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -4944,31 +5354,31 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>889.6799999999999</v>
+        <v>2138.8236</v>
       </c>
       <c r="E10" t="n">
-        <v>878.942</v>
+        <v>312.2463</v>
       </c>
       <c r="F10" t="n">
-        <v>1176.5871</v>
+        <v>417.9854</v>
       </c>
       <c r="G10" t="n">
-        <v>1176.7041</v>
+        <v>418.027</v>
       </c>
       <c r="H10" t="n">
-        <v>456.3924</v>
+        <v>162.1345</v>
       </c>
       <c r="I10" t="n">
-        <v>52.0463</v>
+        <v>21.6495</v>
       </c>
       <c r="J10" t="n">
-        <v>52.8381</v>
+        <v>21.9789</v>
       </c>
       <c r="K10" t="n">
-        <v>54.1227</v>
+        <v>22.5132</v>
       </c>
       <c r="L10" t="n">
-        <v>49.7367</v>
+        <v>20.6888</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -4990,13 +5400,13 @@
         <v>0.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>4.808074</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>4.808074</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -5004,14 +5414,14 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>113.2819</v>
+        <v>68.2291</v>
       </c>
       <c r="W10" t="n">
         <v>0.76</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5025,15 +5435,33 @@
       <c r="C11" t="n">
         <v>50</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>2305.5429</v>
+      </c>
+      <c r="E11" t="n">
+        <v>385.029</v>
+      </c>
+      <c r="F11" t="n">
+        <v>473.2573</v>
+      </c>
+      <c r="G11" t="n">
+        <v>487.4857</v>
+      </c>
+      <c r="H11" t="n">
+        <v>177.4287</v>
+      </c>
+      <c r="I11" t="n">
+        <v>22.2944</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.5754</v>
+      </c>
+      <c r="K11" t="n">
+        <v>23.4345</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21.2865</v>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -5054,28 +5482,28 @@
         <v>0.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>4.808082</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>4.808082</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>116.8555</v>
+        <v>71.8027</v>
       </c>
       <c r="W11" t="n">
         <v>0.76</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5089,15 +5517,33 @@
       <c r="C12" t="n">
         <v>55</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>2447.9919</v>
+      </c>
+      <c r="E12" t="n">
+        <v>385.9269</v>
+      </c>
+      <c r="F12" t="n">
+        <v>522.9851</v>
+      </c>
+      <c r="G12" t="n">
+        <v>523.028</v>
+      </c>
+      <c r="H12" t="n">
+        <v>191.7643</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.1416</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.4577</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24.9803</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.0186</v>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -5118,28 +5564,28 @@
         <v>0.7</v>
       </c>
       <c r="R12" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>4.808096</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>4.808096</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>120.4285</v>
+        <v>75.37569999999999</v>
       </c>
       <c r="W12" t="n">
         <v>0.76</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5153,15 +5599,33 @@
       <c r="C13" t="n">
         <v>60</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>2429.4887</v>
+      </c>
+      <c r="E13" t="n">
+        <v>459.9255</v>
+      </c>
+      <c r="F13" t="n">
+        <v>540.3364</v>
+      </c>
+      <c r="G13" t="n">
+        <v>564.3087</v>
+      </c>
+      <c r="H13" t="n">
+        <v>203.0557</v>
+      </c>
+      <c r="I13" t="n">
+        <v>25.5267</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.858</v>
+      </c>
+      <c r="K13" t="n">
+        <v>26.4354</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.236</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -5182,28 +5646,28 @@
         <v>0.7</v>
       </c>
       <c r="R13" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>4.80808</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>4.80808</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>124.0038</v>
+        <v>78.95099999999999</v>
       </c>
       <c r="W13" t="n">
         <v>0.76</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5217,15 +5681,33 @@
       <c r="C14" t="n">
         <v>64</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>2509.2054</v>
+      </c>
+      <c r="E14" t="n">
+        <v>460.5556</v>
+      </c>
+      <c r="F14" t="n">
+        <v>605.5728</v>
+      </c>
+      <c r="G14" t="n">
+        <v>605.6245</v>
+      </c>
+      <c r="H14" t="n">
+        <v>215.8548</v>
+      </c>
+      <c r="I14" t="n">
+        <v>26.3164</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26.701</v>
+      </c>
+      <c r="K14" t="n">
+        <v>27.9047</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.0098</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -5246,28 +5728,28 @@
         <v>0.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>4.808084</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>4.808084</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>126.8627</v>
+        <v>81.8099</v>
       </c>
       <c r="W14" t="n">
         <v>0.76</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5281,15 +5763,33 @@
       <c r="C15" t="n">
         <v>96</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>2616.0206</v>
+      </c>
+      <c r="E15" t="n">
+        <v>635.3608</v>
+      </c>
+      <c r="F15" t="n">
+        <v>880.9554000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>881.0701</v>
+      </c>
+      <c r="H15" t="n">
+        <v>424.6952</v>
+      </c>
+      <c r="I15" t="n">
+        <v>29.0945</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.4931</v>
+      </c>
+      <c r="K15" t="n">
+        <v>15310.7677</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29.8437</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -5310,28 +5810,28 @@
         <v>0.7</v>
       </c>
       <c r="R15" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>4.808072</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>4.808072</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>149.7383</v>
+        <v>104.6856</v>
       </c>
       <c r="W15" t="n">
         <v>0.76</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5374,13 +5874,13 @@
         <v>0.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>4.808076</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -5388,14 +5888,14 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>172.612</v>
+        <v>127.5593</v>
       </c>
       <c r="W16" t="n">
         <v>0.76</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5410,31 +5910,31 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>228.882</v>
+        <v>515.8745</v>
       </c>
       <c r="E17" t="n">
-        <v>284.0852</v>
+        <v>102.017</v>
       </c>
       <c r="F17" t="n">
-        <v>348.3052</v>
+        <v>125.0788</v>
       </c>
       <c r="G17" t="n">
-        <v>358.7558</v>
+        <v>128.8317</v>
       </c>
       <c r="H17" t="n">
-        <v>178.3716</v>
+        <v>64.0545</v>
       </c>
       <c r="I17" t="n">
-        <v>22.0722</v>
+        <v>9.792899999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>22.4121</v>
+        <v>9.9437</v>
       </c>
       <c r="K17" t="n">
-        <v>23.7366</v>
+        <v>10.5314</v>
       </c>
       <c r="L17" t="n">
-        <v>21.5633</v>
+        <v>9.5672</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5456,13 +5956,13 @@
         <v>0.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>4.507777</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>4.507777</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -5470,14 +5970,14 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>85.88030000000001</v>
+        <v>40.8276</v>
       </c>
       <c r="W17" t="n">
         <v>0.76</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5492,31 +5992,31 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>350.3424</v>
+        <v>789.6326</v>
       </c>
       <c r="E18" t="n">
-        <v>487.7536</v>
+        <v>175.1557</v>
       </c>
       <c r="F18" t="n">
-        <v>569.8938000000001</v>
+        <v>204.6528</v>
       </c>
       <c r="G18" t="n">
-        <v>569.9290999999999</v>
+        <v>204.6655</v>
       </c>
       <c r="H18" t="n">
-        <v>242.6886</v>
+        <v>87.1512</v>
       </c>
       <c r="I18" t="n">
-        <v>28.9931</v>
+        <v>12.8636</v>
       </c>
       <c r="J18" t="n">
-        <v>29.5526</v>
+        <v>13.1118</v>
       </c>
       <c r="K18" t="n">
-        <v>30.2559</v>
+        <v>13.4239</v>
       </c>
       <c r="L18" t="n">
-        <v>28.1559</v>
+        <v>12.4921</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5538,13 +6038,13 @@
         <v>0.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4.507777</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>4.507777</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -5552,14 +6052,14 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>90.6459</v>
+        <v>45.5932</v>
       </c>
       <c r="W18" t="n">
         <v>0.76</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5574,31 +6074,31 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>445.6954</v>
+        <v>1004.5502</v>
       </c>
       <c r="E19" t="n">
-        <v>699.3214</v>
+        <v>251.1311</v>
       </c>
       <c r="F19" t="n">
-        <v>829.5027</v>
+        <v>297.8801</v>
       </c>
       <c r="G19" t="n">
-        <v>829.5391</v>
+        <v>297.8932</v>
       </c>
       <c r="H19" t="n">
-        <v>318.0472</v>
+        <v>114.2129</v>
       </c>
       <c r="I19" t="n">
-        <v>34.2061</v>
+        <v>15.1764</v>
       </c>
       <c r="J19" t="n">
-        <v>34.7298</v>
+        <v>15.4088</v>
       </c>
       <c r="K19" t="n">
-        <v>36.6865</v>
+        <v>16.2769</v>
       </c>
       <c r="L19" t="n">
-        <v>33.1144</v>
+        <v>14.6921</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5620,13 +6120,13 @@
         <v>0.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>4.507788</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>4.507788</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -5634,14 +6134,14 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>95.41119999999999</v>
+        <v>50.3585</v>
       </c>
       <c r="W19" t="n">
         <v>0.76</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5656,31 +6156,31 @@
         <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>529.1626</v>
+        <v>1192.6769</v>
       </c>
       <c r="E20" t="n">
-        <v>909.602</v>
+        <v>326.6444</v>
       </c>
       <c r="F20" t="n">
-        <v>1048.8477</v>
+        <v>376.6484</v>
       </c>
       <c r="G20" t="n">
-        <v>1048.9426</v>
+        <v>376.6825</v>
       </c>
       <c r="H20" t="n">
-        <v>385.6954</v>
+        <v>138.5059</v>
       </c>
       <c r="I20" t="n">
-        <v>38.4502</v>
+        <v>17.0594</v>
       </c>
       <c r="J20" t="n">
-        <v>38.9298</v>
+        <v>17.2722</v>
       </c>
       <c r="K20" t="n">
-        <v>40.4809</v>
+        <v>17.9604</v>
       </c>
       <c r="L20" t="n">
-        <v>37.1265</v>
+        <v>16.4722</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5702,13 +6202,13 @@
         <v>0.7</v>
       </c>
       <c r="R20" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>4.50779</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>4.50779</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5716,14 +6216,14 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>100.1767</v>
+        <v>55.124</v>
       </c>
       <c r="W20" t="n">
         <v>0.76</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5738,31 +6238,31 @@
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>592.2294000000001</v>
+        <v>1334.8189</v>
       </c>
       <c r="E21" t="n">
-        <v>1035.8695</v>
+        <v>371.9879</v>
       </c>
       <c r="F21" t="n">
-        <v>1300.059</v>
+        <v>466.8601</v>
       </c>
       <c r="G21" t="n">
-        <v>1300.069</v>
+        <v>466.8637</v>
       </c>
       <c r="H21" t="n">
-        <v>449.0396</v>
+        <v>161.2532</v>
       </c>
       <c r="I21" t="n">
-        <v>42.8229</v>
+        <v>18.9995</v>
       </c>
       <c r="J21" t="n">
-        <v>43.4236</v>
+        <v>19.2661</v>
       </c>
       <c r="K21" t="n">
-        <v>44.1587</v>
+        <v>19.5923</v>
       </c>
       <c r="L21" t="n">
-        <v>41.4121</v>
+        <v>18.3736</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -5784,13 +6284,13 @@
         <v>0.7</v>
       </c>
       <c r="R21" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>4.507777</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>4.507777</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5798,14 +6298,14 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>104.9428</v>
+        <v>59.8901</v>
       </c>
       <c r="W21" t="n">
         <v>0.76</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5820,31 +6320,31 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>669.4104</v>
+        <v>1508.7811</v>
       </c>
       <c r="E22" t="n">
-        <v>1139.6604</v>
+        <v>409.2599</v>
       </c>
       <c r="F22" t="n">
-        <v>1543.4124</v>
+        <v>554.25</v>
       </c>
       <c r="G22" t="n">
-        <v>1611.1656</v>
+        <v>578.5806</v>
       </c>
       <c r="H22" t="n">
-        <v>514.9842</v>
+        <v>184.9344</v>
       </c>
       <c r="I22" t="n">
-        <v>45.5369</v>
+        <v>20.2036</v>
       </c>
       <c r="J22" t="n">
-        <v>46.1355</v>
+        <v>20.4692</v>
       </c>
       <c r="K22" t="n">
-        <v>47.0064</v>
+        <v>20.8556</v>
       </c>
       <c r="L22" t="n">
-        <v>43.858</v>
+        <v>19.4588</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -5866,13 +6366,13 @@
         <v>0.7</v>
       </c>
       <c r="R22" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>4.507791</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>4.507791</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5880,14 +6380,14 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>109.7077</v>
+        <v>64.6549</v>
       </c>
       <c r="W22" t="n">
         <v>0.76</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5902,31 +6402,31 @@
         <v>35</v>
       </c>
       <c r="D23" t="n">
-        <v>731.391</v>
+        <v>1648.4764</v>
       </c>
       <c r="E23" t="n">
-        <v>1453.4801</v>
+        <v>521.9547</v>
       </c>
       <c r="F23" t="n">
-        <v>1894.5926</v>
+        <v>680.3613</v>
       </c>
       <c r="G23" t="n">
-        <v>1894.6057</v>
+        <v>680.366</v>
       </c>
       <c r="H23" t="n">
-        <v>585.1169</v>
+        <v>210.1195</v>
       </c>
       <c r="I23" t="n">
-        <v>48.5817</v>
+        <v>21.5546</v>
       </c>
       <c r="J23" t="n">
-        <v>49.2347</v>
+        <v>21.8443</v>
       </c>
       <c r="K23" t="n">
-        <v>52.2455</v>
+        <v>23.1801</v>
       </c>
       <c r="L23" t="n">
-        <v>46.6981</v>
+        <v>20.7189</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -5948,13 +6448,13 @@
         <v>0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>4.507784</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4.507784</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5962,14 +6462,14 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>114.4736</v>
+        <v>69.4209</v>
       </c>
       <c r="W23" t="n">
         <v>0.76</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -5983,15 +6483,33 @@
       <c r="C24" t="n">
         <v>40</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>1780.0465</v>
+      </c>
+      <c r="E24" t="n">
+        <v>551.8858</v>
+      </c>
+      <c r="F24" t="n">
+        <v>703.193</v>
+      </c>
+      <c r="G24" t="n">
+        <v>731.6869</v>
+      </c>
+      <c r="H24" t="n">
+        <v>224.6626</v>
+      </c>
+      <c r="I24" t="n">
+        <v>22.8173</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23.1553</v>
+      </c>
+      <c r="K24" t="n">
+        <v>23.7625</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.9267</v>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6012,28 +6530,28 @@
         <v>0.7</v>
       </c>
       <c r="R24" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>4.507783</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4.507783</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>119.2392</v>
+        <v>74.1865</v>
       </c>
       <c r="W24" t="n">
         <v>0.76</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6047,15 +6565,33 @@
       <c r="C25" t="n">
         <v>45</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>1886.4591</v>
+      </c>
+      <c r="E25" t="n">
+        <v>553.7744</v>
+      </c>
+      <c r="F25" t="n">
+        <v>780.5007000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>807.4894</v>
+      </c>
+      <c r="H25" t="n">
+        <v>234.7334</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24.3358</v>
+      </c>
+      <c r="J25" t="n">
+        <v>24.6997</v>
+      </c>
+      <c r="K25" t="n">
+        <v>25.296</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.2579</v>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6076,28 +6612,28 @@
         <v>0.7</v>
       </c>
       <c r="R25" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>4.507794</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>4.507794</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>124.0039</v>
+        <v>78.9512</v>
       </c>
       <c r="W25" t="n">
         <v>0.76</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6111,15 +6647,33 @@
       <c r="C26" t="n">
         <v>50</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>1999.731</v>
+      </c>
+      <c r="E26" t="n">
+        <v>701.5936</v>
+      </c>
+      <c r="F26" t="n">
+        <v>928.939</v>
+      </c>
+      <c r="G26" t="n">
+        <v>960.4342</v>
+      </c>
+      <c r="H26" t="n">
+        <v>279.9549</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25.3521</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25.6529</v>
+      </c>
+      <c r="K26" t="n">
+        <v>154.4295</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24.2678</v>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6140,28 +6694,28 @@
         <v>0.7</v>
       </c>
       <c r="R26" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4.50778</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>4.50778</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>128.7706</v>
+        <v>83.7179</v>
       </c>
       <c r="W26" t="n">
         <v>0.76</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6175,15 +6729,33 @@
       <c r="C27" t="n">
         <v>55</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>1993.7691</v>
+      </c>
+      <c r="E27" t="n">
+        <v>747.8207</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1018.6232</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1042.2373</v>
+      </c>
+      <c r="H27" t="n">
+        <v>364.5633</v>
+      </c>
+      <c r="I27" t="n">
+        <v>25.6989</v>
+      </c>
+      <c r="J27" t="n">
+        <v>25.987</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5359.4519</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25.1164</v>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6204,28 +6776,28 @@
         <v>0.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>4.507789</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>4.507789</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>133.5353</v>
+        <v>88.48260000000001</v>
       </c>
       <c r="W27" t="n">
         <v>0.76</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6239,15 +6811,33 @@
       <c r="C28" t="n">
         <v>60</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>1881.9191</v>
+      </c>
+      <c r="E28" t="n">
+        <v>852.7320999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1150.0248</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1150.0556</v>
+      </c>
+      <c r="H28" t="n">
+        <v>488.5579</v>
+      </c>
+      <c r="I28" t="n">
+        <v>27.4818</v>
+      </c>
+      <c r="J28" t="n">
+        <v>27.9017</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10578.8863</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27.2908</v>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6268,28 +6858,28 @@
         <v>0.7</v>
       </c>
       <c r="R28" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>4.507779</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>4.507779</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>138.3019</v>
+        <v>93.2491</v>
       </c>
       <c r="W28" t="n">
         <v>0.76</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6303,15 +6893,33 @@
       <c r="C29" t="n">
         <v>64</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>1892.8228</v>
+      </c>
+      <c r="E29" t="n">
+        <v>856.1076</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1152.9493</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1153.0851</v>
+      </c>
+      <c r="H29" t="n">
+        <v>516.2663</v>
+      </c>
+      <c r="I29" t="n">
+        <v>28.3218</v>
+      </c>
+      <c r="J29" t="n">
+        <v>28.6674</v>
+      </c>
+      <c r="K29" t="n">
+        <v>12694.5716</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28.2686</v>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6332,28 +6940,28 @@
         <v>0.7</v>
       </c>
       <c r="R29" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>4.507783</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>4.507783</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>142.1139</v>
+        <v>97.0612</v>
       </c>
       <c r="W29" t="n">
         <v>0.76</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6396,13 +7004,13 @@
         <v>0.7</v>
       </c>
       <c r="R30" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>4.507781</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>4.507781</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -6410,14 +7018,14 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>172.6139</v>
+        <v>127.5612</v>
       </c>
       <c r="W30" t="n">
         <v>0.76</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6432,31 +7040,31 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>219.1668</v>
+        <v>445.5583</v>
       </c>
       <c r="E31" t="n">
-        <v>491.8742</v>
+        <v>180.36</v>
       </c>
       <c r="F31" t="n">
-        <v>543.4357</v>
+        <v>199.2666</v>
       </c>
       <c r="G31" t="n">
-        <v>543.4547</v>
+        <v>199.2735</v>
       </c>
       <c r="H31" t="n">
-        <v>220.6331</v>
+        <v>80.9015</v>
       </c>
       <c r="I31" t="n">
-        <v>22.984</v>
+        <v>11.3057</v>
       </c>
       <c r="J31" t="n">
-        <v>23.3729</v>
+        <v>11.497</v>
       </c>
       <c r="K31" t="n">
-        <v>23.9547</v>
+        <v>11.7831</v>
       </c>
       <c r="L31" t="n">
-        <v>22.4496</v>
+        <v>11.0428</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -6478,13 +7086,13 @@
         <v>0.7</v>
       </c>
       <c r="R31" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>4.065929</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>4.065929</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6492,14 +7100,14 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>88.26309999999999</v>
+        <v>43.2104</v>
       </c>
       <c r="W31" t="n">
         <v>0.76</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6514,31 +7122,31 @@
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>328.1736</v>
+        <v>667.1682</v>
       </c>
       <c r="E32" t="n">
-        <v>963.4018</v>
+        <v>353.2593</v>
       </c>
       <c r="F32" t="n">
-        <v>1094.7387</v>
+        <v>401.4179</v>
       </c>
       <c r="G32" t="n">
-        <v>1094.7767</v>
+        <v>401.4318</v>
       </c>
       <c r="H32" t="n">
-        <v>358.1281</v>
+        <v>131.3181</v>
       </c>
       <c r="I32" t="n">
-        <v>30.609</v>
+        <v>15.0562</v>
       </c>
       <c r="J32" t="n">
-        <v>30.9959</v>
+        <v>15.2466</v>
       </c>
       <c r="K32" t="n">
-        <v>31.4653</v>
+        <v>15.4775</v>
       </c>
       <c r="L32" t="n">
-        <v>29.8341</v>
+        <v>14.6751</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -6560,13 +7168,13 @@
         <v>0.7</v>
       </c>
       <c r="R32" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>4.065947</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>4.065947</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -6574,14 +7182,14 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>95.4111</v>
+        <v>50.3584</v>
       </c>
       <c r="W32" t="n">
         <v>0.76</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6596,31 +7204,31 @@
         <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>414.9276</v>
+        <v>843.5339</v>
       </c>
       <c r="E33" t="n">
-        <v>1307.7606</v>
+        <v>479.5285</v>
       </c>
       <c r="F33" t="n">
-        <v>1644.9661</v>
+        <v>603.1748</v>
       </c>
       <c r="G33" t="n">
-        <v>1677.9799</v>
+        <v>615.2802</v>
       </c>
       <c r="H33" t="n">
-        <v>484.686</v>
+        <v>177.7242</v>
       </c>
       <c r="I33" t="n">
-        <v>36.1726</v>
+        <v>17.793</v>
       </c>
       <c r="J33" t="n">
-        <v>36.7582</v>
+        <v>18.0811</v>
       </c>
       <c r="K33" t="n">
-        <v>37.6713</v>
+        <v>18.5302</v>
       </c>
       <c r="L33" t="n">
-        <v>35.2197</v>
+        <v>17.3243</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -6642,13 +7250,13 @@
         <v>0.7</v>
       </c>
       <c r="R33" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>4.065933</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>4.065933</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -6656,14 +7264,14 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>102.5598</v>
+        <v>57.5071</v>
       </c>
       <c r="W33" t="n">
         <v>0.76</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6678,31 +7286,31 @@
         <v>20</v>
       </c>
       <c r="D34" t="n">
-        <v>493.4418</v>
+        <v>1003.1496</v>
       </c>
       <c r="E34" t="n">
-        <v>1685.8243</v>
+        <v>618.1566</v>
       </c>
       <c r="F34" t="n">
-        <v>2140.2719</v>
+        <v>784.7931</v>
       </c>
       <c r="G34" t="n">
-        <v>2184.4688</v>
+        <v>800.9992</v>
       </c>
       <c r="H34" t="n">
-        <v>597.5934</v>
+        <v>219.125</v>
       </c>
       <c r="I34" t="n">
-        <v>40.488</v>
+        <v>19.9157</v>
       </c>
       <c r="J34" t="n">
-        <v>40.9271</v>
+        <v>20.1317</v>
       </c>
       <c r="K34" t="n">
-        <v>41.7081</v>
+        <v>20.5159</v>
       </c>
       <c r="L34" t="n">
-        <v>39.3424</v>
+        <v>19.3522</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -6724,13 +7332,13 @@
         <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>4.065929</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>4.065929</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -6738,14 +7346,14 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>109.7084</v>
+        <v>64.6557</v>
       </c>
       <c r="W34" t="n">
         <v>0.76</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6759,15 +7367,33 @@
       <c r="C35" t="n">
         <v>25</v>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>1109.2924</v>
+      </c>
+      <c r="E35" t="n">
+        <v>717.9503</v>
+      </c>
+      <c r="F35" t="n">
+        <v>934.3268</v>
+      </c>
+      <c r="G35" t="n">
+        <v>934.3771</v>
+      </c>
+      <c r="H35" t="n">
+        <v>250.2097</v>
+      </c>
+      <c r="I35" t="n">
+        <v>22.5882</v>
+      </c>
+      <c r="J35" t="n">
+        <v>22.9177</v>
+      </c>
+      <c r="K35" t="n">
+        <v>23.5296</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.8628</v>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6788,28 +7414,28 @@
         <v>0.7</v>
       </c>
       <c r="R35" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>4.065934</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>4.065934</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>116.8566</v>
+        <v>71.8038</v>
       </c>
       <c r="W35" t="n">
         <v>0.76</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6823,15 +7449,33 @@
       <c r="C36" t="n">
         <v>30</v>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>1232.1233</v>
+      </c>
+      <c r="E36" t="n">
+        <v>902.1943</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1196.8649</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1196.877</v>
+      </c>
+      <c r="H36" t="n">
+        <v>310.3734</v>
+      </c>
+      <c r="I36" t="n">
+        <v>24.2782</v>
+      </c>
+      <c r="J36" t="n">
+        <v>24.5737</v>
+      </c>
+      <c r="K36" t="n">
+        <v>25.0129</v>
+      </c>
+      <c r="L36" t="n">
+        <v>23.491</v>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6852,28 +7496,28 @@
         <v>0.7</v>
       </c>
       <c r="R36" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>4.065947</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>4.065947</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>124.0039</v>
+        <v>78.9512</v>
       </c>
       <c r="W36" t="n">
         <v>0.76</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6887,15 +7531,33 @@
       <c r="C37" t="n">
         <v>35</v>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>1255.3088</v>
+      </c>
+      <c r="E37" t="n">
+        <v>983.3524</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1362.493</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1365.1551</v>
+      </c>
+      <c r="H37" t="n">
+        <v>457.9776</v>
+      </c>
+      <c r="I37" t="n">
+        <v>25.7305</v>
+      </c>
+      <c r="J37" t="n">
+        <v>26.0173</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5218.9973</v>
+      </c>
+      <c r="L37" t="n">
+        <v>25.2344</v>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6916,28 +7578,28 @@
         <v>0.7</v>
       </c>
       <c r="R37" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4.065929</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>4.065929</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>131.1537</v>
+        <v>86.101</v>
       </c>
       <c r="W37" t="n">
         <v>0.76</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -6951,15 +7613,33 @@
       <c r="C38" t="n">
         <v>40</v>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>1167.9158</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1147.9973</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1591.3488</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1604.2486</v>
+      </c>
+      <c r="H38" t="n">
+        <v>754.0585</v>
+      </c>
+      <c r="I38" t="n">
+        <v>26.5636</v>
+      </c>
+      <c r="J38" t="n">
+        <v>26.8298</v>
+      </c>
+      <c r="K38" t="n">
+        <v>15553.3179</v>
+      </c>
+      <c r="L38" t="n">
+        <v>27.0927</v>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -6980,28 +7660,28 @@
         <v>0.7</v>
       </c>
       <c r="R38" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4.065936</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>4.065936</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>138.3014</v>
+        <v>93.2487</v>
       </c>
       <c r="W38" t="n">
         <v>0.76</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7015,15 +7695,33 @@
       <c r="C39" t="n">
         <v>45</v>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>1110.9159</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1505.3749</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1775.4284</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1800.3636</v>
+      </c>
+      <c r="H39" t="n">
+        <v>937.8341</v>
+      </c>
+      <c r="I39" t="n">
+        <v>27.5134</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27.9237</v>
+      </c>
+      <c r="K39" t="n">
+        <v>23058.9121</v>
+      </c>
+      <c r="L39" t="n">
+        <v>29.1632</v>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7044,28 +7742,28 @@
         <v>0.7</v>
       </c>
       <c r="R39" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>4.065939</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>4.065939</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>145.4494</v>
+        <v>100.3966</v>
       </c>
       <c r="W39" t="n">
         <v>0.76</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7079,15 +7777,33 @@
       <c r="C40" t="n">
         <v>50</v>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>1089.2495</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1818.0268</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16999.2539</v>
+      </c>
+      <c r="G40" t="n">
+        <v>17019.1219</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1653.8255</v>
+      </c>
+      <c r="I40" t="n">
+        <v>18.5361</v>
+      </c>
+      <c r="J40" t="n">
+        <v>19.5461</v>
+      </c>
+      <c r="K40" t="n">
+        <v>24.3325</v>
+      </c>
+      <c r="L40" t="n">
+        <v>16.2061</v>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7108,28 +7824,28 @@
         <v>0.7</v>
       </c>
       <c r="R40" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>4.065932</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>4.065932</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>152.5986</v>
+        <v>107.5459</v>
       </c>
       <c r="W40" t="n">
         <v>0.76</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7144,31 +7860,31 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>201.4016</v>
+        <v>355.235</v>
       </c>
       <c r="E41" t="n">
-        <v>997.5291</v>
+        <v>380.3571</v>
       </c>
       <c r="F41" t="n">
-        <v>1149.591</v>
+        <v>438.3382</v>
       </c>
       <c r="G41" t="n">
-        <v>1160.0062</v>
+        <v>442.3095</v>
       </c>
       <c r="H41" t="n">
-        <v>343.4457</v>
+        <v>130.9556</v>
       </c>
       <c r="I41" t="n">
-        <v>24.8123</v>
+        <v>14.0674</v>
       </c>
       <c r="J41" t="n">
-        <v>25.1823</v>
+        <v>14.2772</v>
       </c>
       <c r="K41" t="n">
-        <v>25.7769</v>
+        <v>14.6143</v>
       </c>
       <c r="L41" t="n">
-        <v>24.1789</v>
+        <v>13.7083</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7190,13 +7906,13 @@
         <v>0.7</v>
       </c>
       <c r="R41" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3.527629</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>3.527629</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -7204,14 +7920,14 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>93.0286</v>
+        <v>47.9759</v>
       </c>
       <c r="W41" t="n">
         <v>0.76</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7226,31 +7942,31 @@
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>301.416</v>
+        <v>531.6409</v>
       </c>
       <c r="E42" t="n">
-        <v>1778.5835</v>
+        <v>678.1726</v>
       </c>
       <c r="F42" t="n">
-        <v>2253.5491</v>
+        <v>859.2766</v>
       </c>
       <c r="G42" t="n">
-        <v>2275.2536</v>
+        <v>867.5525</v>
       </c>
       <c r="H42" t="n">
-        <v>603.5616</v>
+        <v>230.1376</v>
       </c>
       <c r="I42" t="n">
-        <v>32.7672</v>
+        <v>18.5775</v>
       </c>
       <c r="J42" t="n">
-        <v>33.252</v>
+        <v>18.8524</v>
       </c>
       <c r="K42" t="n">
-        <v>34.4031</v>
+        <v>19.505</v>
       </c>
       <c r="L42" t="n">
-        <v>31.9847</v>
+        <v>18.1339</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7272,13 +7988,13 @@
         <v>0.7</v>
       </c>
       <c r="R42" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3.527622</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>3.527622</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -7286,14 +8002,14 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>104.9428</v>
+        <v>59.8901</v>
       </c>
       <c r="W42" t="n">
         <v>0.76</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7307,15 +8023,33 @@
       <c r="C43" t="n">
         <v>15</v>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>656.6005</v>
+      </c>
+      <c r="E43" t="n">
+        <v>892.0945</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1196.8289</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1209.509</v>
+      </c>
+      <c r="H43" t="n">
+        <v>304.0924</v>
+      </c>
+      <c r="I43" t="n">
+        <v>22.5307</v>
+      </c>
+      <c r="J43" t="n">
+        <v>22.826</v>
+      </c>
+      <c r="K43" t="n">
+        <v>23.1096</v>
+      </c>
+      <c r="L43" t="n">
+        <v>21.9152</v>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7336,28 +8070,28 @@
         <v>0.7</v>
       </c>
       <c r="R43" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>3.527637</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>3.527637</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>116.8558</v>
+        <v>71.8031</v>
       </c>
       <c r="W43" t="n">
         <v>0.76</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7371,15 +8105,33 @@
       <c r="C44" t="n">
         <v>20</v>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>771.4701</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1187.0826</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1617.9779</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1635.6113</v>
+      </c>
+      <c r="H44" t="n">
+        <v>394.8924</v>
+      </c>
+      <c r="I44" t="n">
+        <v>25.3324</v>
+      </c>
+      <c r="J44" t="n">
+        <v>25.716</v>
+      </c>
+      <c r="K44" t="n">
+        <v>26.3765</v>
+      </c>
+      <c r="L44" t="n">
+        <v>24.6882</v>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7400,28 +8152,28 @@
         <v>0.7</v>
       </c>
       <c r="R44" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>3.527622</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>3.527622</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>128.7709</v>
+        <v>83.7182</v>
       </c>
       <c r="W44" t="n">
         <v>0.76</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7435,15 +8187,33 @@
       <c r="C45" t="n">
         <v>25</v>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>587.977</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2039.4481</v>
+      </c>
+      <c r="F45" t="n">
+        <v>15262.4147</v>
+      </c>
+      <c r="G45" t="n">
+        <v>15370.5463</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1701.8239</v>
+      </c>
+      <c r="I45" t="n">
+        <v>14.6198</v>
+      </c>
+      <c r="J45" t="n">
+        <v>23.2814</v>
+      </c>
+      <c r="K45" t="n">
+        <v>25.9653</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12.6768</v>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7464,28 +8234,28 @@
         <v>0.7</v>
       </c>
       <c r="R45" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3.527622</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>3.527622</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>140.685</v>
+        <v>95.6323</v>
       </c>
       <c r="W45" t="n">
         <v>0.76</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7500,31 +8270,31 @@
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>188.5368</v>
+        <v>302.7765</v>
       </c>
       <c r="E46" t="n">
-        <v>1396.6343</v>
+        <v>552.0331</v>
       </c>
       <c r="F46" t="n">
-        <v>1700.5476</v>
+        <v>672.1578</v>
       </c>
       <c r="G46" t="n">
-        <v>1720.7945</v>
+        <v>680.1606</v>
       </c>
       <c r="H46" t="n">
-        <v>491.6248</v>
+        <v>194.3194</v>
       </c>
       <c r="I46" t="n">
-        <v>26.1791</v>
+        <v>16.3015</v>
       </c>
       <c r="J46" t="n">
-        <v>26.5453</v>
+        <v>16.5296</v>
       </c>
       <c r="K46" t="n">
-        <v>27.0334</v>
+        <v>16.8335</v>
       </c>
       <c r="L46" t="n">
-        <v>25.6158</v>
+        <v>15.9508</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -7546,13 +8316,13 @@
         <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3.211856</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>3.211856</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7560,14 +8330,14 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>97.7944</v>
+        <v>52.7416</v>
       </c>
       <c r="W46" t="n">
         <v>0.76</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7582,31 +8352,31 @@
         <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>279.1078</v>
+        <v>448.227</v>
       </c>
       <c r="E47" t="n">
-        <v>2533.6366</v>
+        <v>1001.4443</v>
       </c>
       <c r="F47" t="n">
-        <v>3390.5521</v>
+        <v>1340.1483</v>
       </c>
       <c r="G47" t="n">
-        <v>3479.2292</v>
+        <v>1375.1988</v>
       </c>
       <c r="H47" t="n">
-        <v>833.0599</v>
+        <v>329.275</v>
       </c>
       <c r="I47" t="n">
-        <v>34.7983</v>
+        <v>21.6687</v>
       </c>
       <c r="J47" t="n">
-        <v>35.2204</v>
+        <v>21.9315</v>
       </c>
       <c r="K47" t="n">
-        <v>37.0438</v>
+        <v>23.0669</v>
       </c>
       <c r="L47" t="n">
-        <v>34.0762</v>
+        <v>21.219</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7628,13 +8398,13 @@
         <v>0.7</v>
       </c>
       <c r="R47" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>3.211856</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>3.211856</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7642,14 +8412,14 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>114.4741</v>
+        <v>69.4213</v>
       </c>
       <c r="W47" t="n">
         <v>0.76</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7663,15 +8433,33 @@
       <c r="C48" t="n">
         <v>15</v>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>468.7545</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1492.555</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2023.0902</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2052.9967</v>
+      </c>
+      <c r="H48" t="n">
+        <v>640.5148</v>
+      </c>
+      <c r="I48" t="n">
+        <v>26.2599</v>
+      </c>
+      <c r="J48" t="n">
+        <v>26.5063</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10369.6218</v>
+      </c>
+      <c r="L48" t="n">
+        <v>26.3443</v>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7692,28 +8480,28 @@
         <v>0.7</v>
       </c>
       <c r="R48" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>3.211857</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>3.211857</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>131.1536</v>
+        <v>86.1009</v>
       </c>
       <c r="W48" t="n">
         <v>0.76</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7727,15 +8515,33 @@
       <c r="C49" t="n">
         <v>20</v>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>429.9294</v>
+      </c>
+      <c r="E49" t="n">
+        <v>14890.2638</v>
+      </c>
+      <c r="F49" t="n">
+        <v>15080.6261</v>
+      </c>
+      <c r="G49" t="n">
+        <v>15080.6602</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3242.7432</v>
+      </c>
+      <c r="I49" t="n">
+        <v>16.3499</v>
+      </c>
+      <c r="J49" t="n">
+        <v>21.264</v>
+      </c>
+      <c r="K49" t="n">
+        <v>25.4143</v>
+      </c>
+      <c r="L49" t="n">
+        <v>14.7766</v>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7756,28 +8562,28 @@
         <v>0.7</v>
       </c>
       <c r="R49" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>3.211863</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>3.211863</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>147.8323</v>
+        <v>102.7796</v>
       </c>
       <c r="W49" t="n">
         <v>0.76</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7792,31 +8598,31 @@
         <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>173.255</v>
+        <v>260.2528</v>
       </c>
       <c r="E50" t="n">
-        <v>1889.7381</v>
+        <v>772.1543</v>
       </c>
       <c r="F50" t="n">
-        <v>2348.2401</v>
+        <v>959.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2392.4598</v>
+        <v>977.5683</v>
       </c>
       <c r="H50" t="n">
-        <v>627.9517</v>
+        <v>256.5835</v>
       </c>
       <c r="I50" t="n">
-        <v>28.2354</v>
+        <v>18.7968</v>
       </c>
       <c r="J50" t="n">
-        <v>28.616</v>
+        <v>19.0502</v>
       </c>
       <c r="K50" t="n">
-        <v>31.5981</v>
+        <v>21.0354</v>
       </c>
       <c r="L50" t="n">
-        <v>27.6483</v>
+        <v>18.4059</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -7838,13 +8644,13 @@
         <v>0.7</v>
       </c>
       <c r="R50" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3.004275</v>
       </c>
       <c r="T50" t="n">
-        <v>2</v>
+        <v>3.004275</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7852,14 +8658,14 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>102.5597</v>
+        <v>57.507</v>
       </c>
       <c r="W50" t="n">
         <v>0.76</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7873,15 +8679,33 @@
       <c r="C51" t="n">
         <v>10</v>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>376.5823</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1446.1902</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1908.3893</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1946.4955</v>
+      </c>
+      <c r="H51" t="n">
+        <v>442.0501</v>
+      </c>
+      <c r="I51" t="n">
+        <v>25.5902</v>
+      </c>
+      <c r="J51" t="n">
+        <v>25.9452</v>
+      </c>
+      <c r="K51" t="n">
+        <v>26.548</v>
+      </c>
+      <c r="L51" t="n">
+        <v>24.9964</v>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7902,28 +8726,28 @@
         <v>0.7</v>
       </c>
       <c r="R51" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3.004271</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>3.004271</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>124.0052</v>
+        <v>78.9524</v>
       </c>
       <c r="W51" t="n">
         <v>0.76</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
@@ -7937,15 +8761,33 @@
       <c r="C52" t="n">
         <v>15</v>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>328.4881</v>
+      </c>
+      <c r="E52" t="n">
+        <v>14245.2377</v>
+      </c>
+      <c r="F52" t="n">
+        <v>14848.4421</v>
+      </c>
+      <c r="G52" t="n">
+        <v>14877.2969</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2889.5649</v>
+      </c>
+      <c r="I52" t="n">
+        <v>14.9061</v>
+      </c>
+      <c r="J52" t="n">
+        <v>21.0217</v>
+      </c>
+      <c r="K52" t="n">
+        <v>25.744</v>
+      </c>
+      <c r="L52" t="n">
+        <v>13.7129</v>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>671B-P800-8测试数据</t>
@@ -7966,28 +8808,28 @@
         <v>0.7</v>
       </c>
       <c r="R52" t="n">
-        <v>2.785714</v>
+        <v>7.928571</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3.00427</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>3.00427</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>memory_infeasible</t>
+          <t>memory_bandwidth</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>145.4505</v>
+        <v>100.3977</v>
       </c>
       <c r="W52" t="n">
         <v>0.76</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>DeepSeek-V3/R1 proxy; public_cloudmatrix384_assumption; runtime=基准</t>
+          <t>DeepSeek-R1/P800 INT8 baseline proxy -&gt; DeepSeek-V4-Flash public 284B/13B; R1 proxy architecture; public_cloudmatrix384_assumption; runtime=基准</t>
         </is>
       </c>
     </row>
